--- a/data/reports/PHASE_9_MIDDAY_MODEL.xlsx
+++ b/data/reports/PHASE_9_MIDDAY_MODEL.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -590,7 +590,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>07</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -610,11 +610,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8">
@@ -860,17 +860,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -880,7 +880,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46">
@@ -1186,7 +1186,7 @@
         <v>11</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9">
@@ -1958,7 +1958,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>015</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1968,7 +1968,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>344</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -2018,7 +2018,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -2138,7 +2138,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>047</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -2218,11 +2218,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>158</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
@@ -2298,7 +2298,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -2398,7 +2398,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>047</t>
+          <t>445</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -2408,7 +2408,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>059</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -2458,7 +2458,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>059</t>
+          <t>178</t>
         </is>
       </c>
       <c r="B110" t="n">
